--- a/data/trans_bre/P19C04-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P19C04-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -0,92</t>
+          <t>-10,33; -0,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 2,3</t>
+          <t>-8,24; 2,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 3,13</t>
+          <t>-5,63; 3,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -1,03</t>
+          <t>-6,57; -0,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-67,32; -7,92</t>
+          <t>-68,24; -4,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,55; 20,86</t>
+          <t>-51,34; 20,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 44,69</t>
+          <t>-50,23; 49,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-64,48; -13,57</t>
+          <t>-62,8; -5,87</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,0; -2,72</t>
+          <t>-13,94; -2,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 1,36</t>
+          <t>-8,46; 1,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,4; -1,75</t>
+          <t>-11,29; -1,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,36; -1,29</t>
+          <t>-8,38; -1,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,03; -20,56</t>
+          <t>-71,14; -16,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,29; 11,58</t>
+          <t>-51,74; 15,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,42; -15,58</t>
+          <t>-74,33; -12,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,39; -13,51</t>
+          <t>-65,56; -13,19</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -0,77</t>
+          <t>-14,12; -0,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,93; -9,55</t>
+          <t>-20,62; -9,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 5,4</t>
+          <t>-9,24; 5,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 9,7</t>
+          <t>-5,8; 11,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,05; -2,4</t>
+          <t>-60,49; -1,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-73,91; -37,79</t>
+          <t>-72,41; -37,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,3; 33,16</t>
+          <t>-47,28; 33,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,18; 210,89</t>
+          <t>-39,85; 347,11</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,48; -4,98</t>
+          <t>-13,37; -5,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,26; -12,68</t>
+          <t>-21,32; -12,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -5,2</t>
+          <t>-12,97; -4,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,73; -6,34</t>
+          <t>-15,13; -6,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,62; -20,66</t>
+          <t>-49,17; -20,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,57; -41,26</t>
+          <t>-61,7; -41,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,44; -25,23</t>
+          <t>-54,63; -23,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,92; -36,96</t>
+          <t>-76,49; -37,0</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 2,28</t>
+          <t>-11,11; 2,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,29; -3,98</t>
+          <t>-15,49; -3,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,33; -6,59</t>
+          <t>-17,12; -6,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,33; -5,88</t>
+          <t>-17,15; -6,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 10,72</t>
+          <t>-38,99; 11,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,86; -12,82</t>
+          <t>-41,36; -11,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-56,23; -26,96</t>
+          <t>-56,31; -27,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,22; -25,02</t>
+          <t>-59,17; -27,12</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 10,88</t>
+          <t>1,1; 10,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,88; 15,93</t>
+          <t>6,2; 15,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 11,48</t>
+          <t>2,31; 11,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 10,52</t>
+          <t>-1,86; 10,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,33; 176,71</t>
+          <t>7,24; 166,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,86; 257,07</t>
+          <t>43,86; 234,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,63; 171,45</t>
+          <t>15,49; 175,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 316,85</t>
+          <t>-14,89; 290,2</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,24; -3,0</t>
+          <t>-7,38; -3,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,35; -4,95</t>
+          <t>-9,4; -5,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -2,79</t>
+          <t>-6,86; -2,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,02; -0,24</t>
+          <t>-6,01; -0,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,46; -15,9</t>
+          <t>-34,59; -17,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-36,35; -21,12</t>
+          <t>-36,17; -21,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-36,38; -16,85</t>
+          <t>-36,5; -17,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-40,1; -5,37</t>
+          <t>-39,17; -3,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C04-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P19C04-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,67</t>
+          <t>-3,77</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-43,68%</t>
+          <t>-44,69%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,33; -0,86</t>
+          <t>-10,18; -1,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 2,25</t>
+          <t>-7,85; 3,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 3,08</t>
+          <t>-5,67; 2,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,57; -0,46</t>
+          <t>-7,02; -1,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,24; -4,93</t>
+          <t>-67,74; -9,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,34; 20,92</t>
+          <t>-49,96; 30,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,23; 49,16</t>
+          <t>-52,35; 37,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-62,8; -5,87</t>
+          <t>-66,16; -15,88</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,44</t>
+          <t>-4,25</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-43,43%</t>
+          <t>-42,08%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,94; -2,72</t>
+          <t>-13,08; -2,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 1,86</t>
+          <t>-9,11; 2,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -1,2</t>
+          <t>-11,98; -1,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,38; -1,31</t>
+          <t>-7,67; -0,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,14; -16,49</t>
+          <t>-70,17; -19,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,74; 15,45</t>
+          <t>-51,87; 19,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,33; -12,27</t>
+          <t>-73,59; -16,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,56; -13,19</t>
+          <t>-62,99; -10,16</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>-5,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>-33,8%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,12; -0,52</t>
+          <t>-14,22; -0,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,62; -9,04</t>
+          <t>-20,66; -9,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 5,5</t>
+          <t>-9,93; 6,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 11,57</t>
+          <t>-10,25; -0,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,49; -1,91</t>
+          <t>-61,51; -0,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-72,41; -37,97</t>
+          <t>-71,95; -38,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,28; 33,93</t>
+          <t>-51,05; 38,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 347,11</t>
+          <t>-55,99; 2,19</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-9,88</t>
+          <t>-8,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-54,1%</t>
+          <t>-42,46%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,37; -5,1</t>
+          <t>-13,22; -4,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,32; -12,72</t>
+          <t>-21,27; -12,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,97; -4,94</t>
+          <t>-12,58; -5,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,13; -6,25</t>
+          <t>-11,0; -5,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,17; -20,88</t>
+          <t>-49,07; -20,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,7; -41,09</t>
+          <t>-61,49; -41,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,63; -23,77</t>
+          <t>-54,33; -24,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,49; -37,0</t>
+          <t>-53,03; -29,22</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-11,09</t>
+          <t>-11,13</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-41,03%</t>
+          <t>-38,38%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 2,22</t>
+          <t>-11,15; 2,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -3,48</t>
+          <t>-15,38; -3,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,12; -6,98</t>
+          <t>-17,36; -7,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,15; -6,32</t>
+          <t>-16,11; -6,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,99; 11,5</t>
+          <t>-38,29; 9,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,36; -11,57</t>
+          <t>-41,35; -11,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-56,31; -27,35</t>
+          <t>-56,83; -28,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-59,17; -27,12</t>
+          <t>-49,21; -25,69</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,26</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>82,54%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,73</t>
+          <t>1,46; 11,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 15,23</t>
+          <t>6,4; 15,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 11,64</t>
+          <t>2,4; 11,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 10,49</t>
+          <t>-1,37; 9,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,24; 166,87</t>
+          <t>10,63; 189,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43,86; 234,96</t>
+          <t>49,64; 254,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,49; 175,69</t>
+          <t>17,15; 180,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 290,2</t>
+          <t>-11,88; 277,32</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,74</t>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-26,24%</t>
+          <t>-29,25%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,38; -3,25</t>
+          <t>-7,37; -3,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -5,11</t>
+          <t>-9,3; -4,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,86; -2,92</t>
+          <t>-6,97; -2,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,01; -0,05</t>
+          <t>-6,44; -3,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,59; -17,16</t>
+          <t>-34,79; -16,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-36,17; -21,69</t>
+          <t>-35,79; -20,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-36,5; -17,74</t>
+          <t>-36,31; -16,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-39,17; -3,47</t>
+          <t>-37,3; -21,69</t>
         </is>
       </c>
     </row>
